--- a/results/tables/19_FINAL_RESULTS.xlsx
+++ b/results/tables/19_FINAL_RESULTS.xlsx
@@ -6,8 +6,8 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="RRUI_all_inference" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Article_table" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Article_table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_inference" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Final_coefficients" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
@@ -19,76 +19,79 @@
     <t xml:space="preserve">Model</t>
   </si>
   <si>
+    <t xml:space="preserve">Specification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta_RRUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clustered_SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clustered_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR2_SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR2_df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR2_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WCB_Rademacher_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WCB_Rademacher_p_strict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WCB_Webb_p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Climate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRUI + climate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Climate + livestock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRUI + climate + livestock</t>
+  </si>
+  <si>
     <t xml:space="preserve">Inference</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta_RRUI</t>
-  </si>
-  <si>
     <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">P_value</t>
   </si>
   <si>
-    <t xml:space="preserve">CI_lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI_upper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clusters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clustered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCB Rademacher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCB Webb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Climate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Climate + livestock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Specification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clustered_SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clustered_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CR2_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCB_Rademacher_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WCB_Webb_p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRUI + climate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRUI + climate + livestock</t>
+    <t xml:space="preserve">Clustered (fixest CRV1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR2 (Satterthwaite)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WCB Rademacher (exact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WCB Webb (exact)</t>
   </si>
   <si>
     <t xml:space="preserve">Variable</t>
@@ -97,16 +100,13 @@
     <t xml:space="preserve">Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">CR2_SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precipitation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Livestock units</t>
+    <t xml:space="preserve">precip_mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temp_c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livestock_units</t>
   </si>
 </sst>
 </file>
@@ -463,320 +463,139 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0183959</v>
+        <v>-0.0183959007727674</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01110761</v>
+        <v>0.0111076080763295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1730322</v>
+        <v>0.173032204141352</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.04923556</v>
+        <v>0.0112766031492685</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01244376</v>
+        <v>2.34579070708562</v>
       </c>
       <c r="H2" t="n">
-        <v>65</v>
+        <v>0.225879716078378</v>
       </c>
       <c r="I2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.21167695473251</v>
+      </c>
+      <c r="L2" t="n">
+        <v>65</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0183959</v>
+        <v>-0.0162609770240871</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0101</v>
+        <v>0.00892256574924001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="F3"/>
-      <c r="G3"/>
+        <v>0.14247018656341</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0106352518672644</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.34069772526282</v>
+      </c>
       <c r="H3" t="n">
-        <v>65</v>
+        <v>0.248020620666538</v>
       </c>
       <c r="I3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.108796296296296</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65</v>
+      </c>
+      <c r="M3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0183959</v>
-      </c>
-      <c r="D4"/>
+        <v>-0.0171577292272654</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0104543457635575</v>
+      </c>
       <c r="E4" t="n">
-        <v>0.1875</v>
+        <v>0.176098893067961</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08442475</v>
+        <v>0.0123895461213593</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01554846</v>
+        <v>2.44385191482427</v>
       </c>
       <c r="H4" t="n">
-        <v>65</v>
+        <v>0.278965500316458</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.0183959</v>
-      </c>
-      <c r="D5"/>
-      <c r="E5" t="n">
-        <v>0.2042</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.0984</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0168</v>
-      </c>
-      <c r="H5" t="n">
-        <v>65</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.01626098</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.008922566</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.1424702</v>
-      </c>
-      <c r="F6"/>
-      <c r="G6"/>
-      <c r="H6" t="n">
-        <v>65</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.01626098</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.00915</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="F7"/>
-      <c r="G7"/>
-      <c r="H7" t="n">
-        <v>65</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.01626098</v>
-      </c>
-      <c r="D8"/>
-      <c r="E8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.0625</v>
       </c>
-      <c r="F8" t="n">
-        <v>-0.07638674</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.007041601</v>
-      </c>
-      <c r="H8" t="n">
-        <v>65</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.01626098</v>
-      </c>
-      <c r="D9"/>
-      <c r="E9" t="n">
-        <v>0.1083108</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.07432589</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.006831563</v>
-      </c>
-      <c r="H9" t="n">
-        <v>65</v>
-      </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.01791425</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.010618058</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.1668497</v>
-      </c>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10" t="n">
-        <v>65</v>
-      </c>
-      <c r="I10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.01791425</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.018852245</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.5162379</v>
-      </c>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11" t="n">
-        <v>65</v>
-      </c>
-      <c r="I11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.01791425</v>
-      </c>
-      <c r="D12"/>
-      <c r="E12" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.04805527</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.005300286</v>
-      </c>
-      <c r="H12" t="n">
-        <v>65</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.01791425</v>
-      </c>
-      <c r="D13"/>
-      <c r="E13" t="n">
-        <v>0.1194119</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-0.05846618</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.005885138</v>
-      </c>
-      <c r="H13" t="n">
-        <v>65</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="K4" t="n">
+        <v>0.131172839506173</v>
+      </c>
+      <c r="L4" t="n">
+        <v>65</v>
+      </c>
+      <c r="M4" t="n">
         <v>5</v>
       </c>
     </row>
@@ -793,117 +612,288 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="n">
-        <v>-0.0183959</v>
-      </c>
       <c r="C2" t="n">
-        <v>0.01110761</v>
+        <v>-0.0183959007727674</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1730322</v>
+        <v>0.0111076080763295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.258</v>
+        <v>0.173032204141352</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1875</v>
+        <v>65</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2042</v>
-      </c>
-      <c r="H2" t="n">
-        <v>65</v>
-      </c>
-      <c r="I2" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="n">
-        <v>-0.01626098</v>
-      </c>
       <c r="C3" t="n">
-        <v>0.008922566</v>
+        <v>-0.0183959007727674</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1424702</v>
+        <v>0.0112766031492685</v>
       </c>
       <c r="E3" t="n">
-        <v>0.326</v>
+        <v>0.225879716078378</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0625</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1083108</v>
-      </c>
-      <c r="H3" t="n">
-        <v>65</v>
-      </c>
-      <c r="I3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="n">
-        <v>-0.01791425</v>
-      </c>
       <c r="C4" t="n">
-        <v>0.010618058</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1668497</v>
-      </c>
+        <v>-0.0183959007727674</v>
+      </c>
+      <c r="D4"/>
       <c r="E4" t="n">
-        <v>0.5162379</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0625</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1194119</v>
-      </c>
-      <c r="H4" t="n">
-        <v>65</v>
-      </c>
-      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.0183959007727674</v>
+      </c>
+      <c r="D5"/>
+      <c r="E5" t="n">
+        <v>0.21167695473251</v>
+      </c>
+      <c r="F5" t="n">
+        <v>65</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0162609770240871</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.00892256574924001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.14247018656341</v>
+      </c>
+      <c r="F6" t="n">
+        <v>65</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0162609770240871</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0106352518672644</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.248020620666538</v>
+      </c>
+      <c r="F7" t="n">
+        <v>65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.0162609770240871</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F8" t="n">
+        <v>65</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.0162609770240871</v>
+      </c>
+      <c r="D9"/>
+      <c r="E9" t="n">
+        <v>0.108796296296296</v>
+      </c>
+      <c r="F9" t="n">
+        <v>65</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.0171577292272654</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0104543457635575</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.176098893067961</v>
+      </c>
+      <c r="F10" t="n">
+        <v>65</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.0171577292272654</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0123895461213593</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.278965500316458</v>
+      </c>
+      <c r="F11" t="n">
+        <v>65</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.0171577292272654</v>
+      </c>
+      <c r="D12"/>
+      <c r="E12" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F12" t="n">
+        <v>65</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.0171577292272654</v>
+      </c>
+      <c r="D13"/>
+      <c r="E13" t="n">
+        <v>0.131172839506173</v>
+      </c>
+      <c r="F13" t="n">
+        <v>65</v>
+      </c>
+      <c r="G13" t="n">
         <v>5</v>
       </c>
     </row>
@@ -920,42 +910,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.01791425</v>
+        <v>-0.0171577292272654</v>
       </c>
       <c r="C2" t="n">
-        <v>0.010618058</v>
+        <v>0.0104543457635575</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1668497</v>
+        <v>0.176098893067961</v>
       </c>
       <c r="E2" t="n">
-        <v>0.018852245</v>
+        <v>0.0123895461213593</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5162379</v>
+        <v>2.44385191482427</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.278965500316458</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.131172839506173</v>
       </c>
     </row>
     <row r="3">
@@ -963,19 +971,28 @@
         <v>28</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0006270414</v>
+        <v>0.000623820651082471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002528048</v>
+        <v>0.000248696152958117</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0681864</v>
+        <v>0.0661727460592482</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002231333</v>
+        <v>0.000265016532654134</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8255973</v>
+        <v>3.42970985247456</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0890340124124235</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.104166666666667</v>
       </c>
     </row>
     <row r="4">
@@ -983,19 +1000,28 @@
         <v>29</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.05585412</v>
+        <v>-0.0557642436252803</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0101486915</v>
+        <v>0.0100674365527475</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0053156</v>
+        <v>0.00519365704657688</v>
       </c>
       <c r="E4" t="n">
-        <v>0.256391894</v>
+        <v>0.0103224549132227</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8634479</v>
+        <v>2.67859783257233</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0165513486876205</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0329218106995885</v>
       </c>
     </row>
     <row r="5">
@@ -1003,19 +1029,28 @@
         <v>30</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.00009970014</v>
+        <v>-0.0000680469738216597</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002564033</v>
+        <v>0.000318307581787583</v>
       </c>
       <c r="D5" t="n">
-        <v>0.717205</v>
+        <v>0.841175373625743</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000855344</v>
+        <v>0.000338719713224403</v>
       </c>
       <c r="F5" t="n">
-        <v>0.926128</v>
+        <v>2.56555360583706</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.855624928094917</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.880658436213992</v>
       </c>
     </row>
   </sheetData>
